--- a/support/Dataset_S6_Satisfaccion_Clientes.xlsx
+++ b/support/Dataset_S6_Satisfaccion_Clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnoutb-my.sharepoint.com/personal/epuerta_utb_edu_co/Documents/Academic/AI Literacy/support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_6D3F027E3055946F4CA7E660A23F07594651153D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BC74C7D-FC29-44A6-B3E7-54F5D8C7EFB8}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_6D3F027E3055946F4CA7E660A23F07594651153D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDAFBB07-AFF7-4F3B-93E8-55ECAB194586}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="satisfaccion_clientes" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="tabla_self_consistency" sheetId="3" r:id="rId3"/>
     <sheet name="datasets_libre_acceso" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">satisfaccion_clientes!$A$4:$I$34</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1040,171 +1043,171 @@
   </cellStyleXfs>
   <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1289,6 +1292,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1479,1015 +1486,1016 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" style="56" customWidth="1"/>
+    <col min="4" max="4" width="18" style="46" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="22" style="56" customWidth="1"/>
+    <col min="7" max="7" width="22" style="46" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="5">
         <v>45323</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="39">
         <v>4</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="4">
         <v>65</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="9">
         <v>45296</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="39">
         <v>4</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="8">
         <v>15</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="5">
         <v>45375</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="44">
         <v>2</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="44">
         <v>239</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="9">
         <v>45312</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="44">
         <v>2</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="44">
         <v>238</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="5">
         <v>45335</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="45">
         <v>3</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="4">
         <v>86</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="9">
         <v>45297</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="44">
         <v>1</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="44">
         <v>246</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="5">
         <v>45362</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="39">
         <v>4</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="4">
         <v>83</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="9">
         <v>45376</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="39">
         <v>4</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="8">
         <v>66</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="5">
         <v>45340</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="39">
         <v>5</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="4">
         <v>79</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="9">
         <v>45339</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="39">
         <v>4</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="8">
         <v>98</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="5">
         <v>45360</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="39">
         <v>4</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="4">
         <v>70</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="9">
         <v>45379</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="45">
         <v>3</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="57">
+      <c r="G16" s="47">
         <v>143</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="5">
         <v>45326</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="49">
+      <c r="D17" s="39">
         <v>5</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="4">
         <v>24</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="9">
         <v>45375</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="39">
         <v>5</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="57">
+      <c r="G18" s="47">
         <v>135</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="5">
         <v>45325</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="39">
         <v>5</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="4">
         <v>43</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="9">
         <v>45366</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="49">
+      <c r="D20" s="39">
         <v>4</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="8">
         <v>110</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="5">
         <v>45303</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="44">
         <v>2</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="4">
         <v>72</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="9">
         <v>45368</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="44">
         <v>2</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="8">
         <v>76</v>
       </c>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="5">
         <v>45362</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="45">
         <v>3</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="4">
         <v>62</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="9">
         <v>45306</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="49">
+      <c r="D24" s="39">
         <v>5</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="8">
         <v>83</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="5">
         <v>45356</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="44">
         <v>2</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="4">
         <v>105</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="9">
         <v>45311</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="49">
+      <c r="D26" s="39">
         <v>5</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="8">
         <v>103</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="5">
         <v>45354</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="49">
+      <c r="D27" s="39">
         <v>4</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="4">
         <v>12</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="9">
         <v>45299</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="49">
+      <c r="D28" s="39">
         <v>5</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="8">
         <v>69</v>
       </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="5">
         <v>45360</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="44">
         <v>1</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="4">
         <v>92</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="9">
         <v>45359</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="49">
+      <c r="D30" s="39">
         <v>4</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="57">
+      <c r="G30" s="47">
         <v>163</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="5">
         <v>45343</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="49">
+      <c r="D31" s="39">
         <v>5</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="58">
+      <c r="G31" s="48">
         <v>179</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="9">
         <v>45323</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="45">
         <v>3</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="8">
         <v>117</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="5">
         <v>45292</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="44">
         <v>1</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="4">
         <v>78</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="9">
         <v>45301</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="44">
         <v>2</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="54">
+      <c r="G34" s="44">
         <v>191</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="24">
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="14">
         <f>AVERAGE(D5:D34)</f>
         <v>3.4333333333333331</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="25">
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="15">
         <f>IFERROR(COUNTIF(H5:H34,"Sí")/COUNTA(H5:H34),0)</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="26">
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="16">
         <f>AVERAGE(G5:G34)</f>
         <v>104.73333333333333</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="6">
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A1:I1"/>
@@ -2519,332 +2527,332 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="22" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="28" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="22" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="22" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="28" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="22" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="15" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2876,324 +2884,324 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
     </row>
     <row r="6" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
     </row>
     <row r="7" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="42"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="42"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="42"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="42"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="32"/>
     </row>
     <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
     </row>
     <row r="20" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
     </row>
     <row r="21" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
     </row>
     <row r="22" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
     </row>
     <row r="23" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="56"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
     </row>
     <row r="25" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="46"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="36"/>
     </row>
     <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="46"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="36"/>
     </row>
     <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="36"/>
     </row>
     <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="46"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="36"/>
     </row>
     <row r="31" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="46"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="36"/>
     </row>
     <row r="32" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="46"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="36"/>
     </row>
     <row r="33" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="49">
+      <c r="B33" s="39">
         <f>SUM(B27:B32)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="49">
+      <c r="C33" s="39">
         <f>SUM(C27:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="49">
+      <c r="D33" s="39">
         <f>SUM(D27:D32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="39">
         <f>SUM(E27:E32)</f>
         <v>0</v>
       </c>
@@ -3230,174 +3238,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="49" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="2" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="41" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="43" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="41" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="43" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="41" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="43" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="51" t="s">
         <v>226</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="3">
